--- a/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,95</t>
+          <t>0,76; 6,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,22</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,2</t>
+          <t>0,77; 4,49</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,29</t>
+          <t>1,97; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,0</t>
+          <t>1,34; 4,22</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,05</t>
+          <t>0,47; 4,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,47</t>
+          <t>0,23; 2,15</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,79</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,87</t>
+          <t>0,29; 1,95</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,02</t>
+          <t>0,57; 1,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,48</t>
+          <t>0,95; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,96</t>
+          <t>0,91; 1,98</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2553</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>430; 3849</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3002</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>905; 5298</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7970</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4953</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3517; 11408</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4477; 14099</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>799; 6876</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4206</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>859; 8048</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4773</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6865</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8217</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1633; 11148</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3692; 12913</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7086; 18619</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12766; 27648</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,76</t>
+          <t>0,77; 6,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,56; 5,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,49</t>
+          <t>0,8; 4,61</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,41</t>
+          <t>1,97; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,22</t>
+          <t>1,29; 4,08</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,04</t>
+          <t>0,48; 4,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,15</t>
+          <t>0,24; 2,12</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,25; 3,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,95</t>
+          <t>0,3; 1,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,98</t>
+          <t>0,57; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,5</t>
+          <t>0,89; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,98</t>
+          <t>0,95; 2,0</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>430; 3849</t>
+          <t>440; 3777</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3002</t>
+          <t>342; 3220</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>905; 5298</t>
+          <t>938; 5445</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 5298</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3517; 11408</t>
+          <t>3501; 11368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4477; 14099</t>
+          <t>4306; 13625</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>799; 6876</t>
+          <t>813; 6964</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4206</t>
+          <t>0; 4310</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>859; 8048</t>
+          <t>881; 7910</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6865</t>
+          <t>0; 6172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 8217</t>
+          <t>766; 10191</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1633; 11148</t>
+          <t>1736; 11311</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3692; 12913</t>
+          <t>3708; 13012</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7086; 18619</t>
+          <t>6626; 17854</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12766; 27648</t>
+          <t>13303; 27969</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,63</t>
+          <t>0,58; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,27</t>
+          <t>0,72; 6,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,61</t>
+          <t>0,75; 4,27</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>1,91; 6,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,38</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,08</t>
+          <t>1,27; 4,16</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,1</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,54; 4,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,12</t>
+          <t>0,26; 2,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,3; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,38</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,98</t>
+          <t>0,34; 2,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,0</t>
+          <t>0,88; 2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,4</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,0</t>
+          <t>0,93; 2,07</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>981</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2175</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>440; 3777</t>
+          <t>289; 2728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>342; 3220</t>
+          <t>371; 3443</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>938; 5445</t>
+          <t>765; 4348</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7091</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5298</t>
+          <t>2922; 9801</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3501; 11368</t>
+          <t>0; 5026</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4306; 13625</t>
+          <t>3764; 12320</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>959</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3762</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>813; 6964</t>
+          <t>0; 5314</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4310</t>
+          <t>918; 7917</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>881; 7910</t>
+          <t>947; 9535</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>5217</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6172</t>
+          <t>879; 8794</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>766; 10191</t>
+          <t>0; 7109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1736; 11311</t>
+          <t>1817; 11870</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18245</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3708; 13012</t>
+          <t>6006; 17843</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6626; 17854</t>
+          <t>3722; 13270</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13303; 27969</t>
+          <t>12043; 26960</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 5,43</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 6,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 6,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 4,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 4,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 2,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 3,05</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 2,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 2,61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 2,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.0195395346383286</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02312437056559579</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02135636433758699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.005754697708207271</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.007184552574845625</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.007507560559869353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>289; 2728</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>371; 3443</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>765; 4348</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.05432284670252745</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.0667097817458652</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.04269269381605982</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.03716276715437927</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.009822651457180453</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02393225904192527</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5682</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7091</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01910632794948321</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01270353468975239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2922; 9801</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5026</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3764; 12320</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.06409936646475127</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03505332429605738</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0415822860139306</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.005004508667603303</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01635341711597908</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.0103638584882083</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3762</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.005357033004822715</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.002608988122839206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5314</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>918; 7917</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>947; 9535</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.02773746318511712</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.04618355020738844</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.02626630128941059</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01142569062890405</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.007675881650604411</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.009682598914532055</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.003046661494005586</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.003372377866007336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>879; 8794</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 7109</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1817; 11870</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.03049596404739574</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02838066648219686</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02202906448318667</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.01598245970611355</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01187869082558752</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.01403503507028383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>10917</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.008792060614115627</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.006033139391511819</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.009263849270876739</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6006; 17843</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3722; 13270</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12043; 26960</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.02612090653749811</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02151036011415169</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02073837530291405</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>981</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1193</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>371</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2728</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3443</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5682</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1408</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7091</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2922</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9801</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5026</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12320</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>959</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>2804</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>918</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5314</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7917</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9535</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3295</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>5217</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>879</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>8794</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>7109</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>11870</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>10917</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>7328</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>18245</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6006</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3722</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>12043</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>17843</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>13270</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>26960</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>